--- a/healthcare_forms/014_hospital_patient_discharge_process_evaluation_form--healthcare_forms.xlsx
+++ b/healthcare_forms/014_hospital_patient_discharge_process_evaluation_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'8-12_hours'}</t>
+          <t>8-12_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '8-12 hours'}</t>
+          <t>8-12 hours</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'0-7_hours'}</t>
+          <t>0-7_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '0-7 hours'}</t>
+          <t>0-7 hours</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'7-16_hours'}</t>
+          <t>7-16_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '7-16 hours'}</t>
+          <t>7-16 hours</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'16-24_hours'}</t>
+          <t>16-24_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '16-24 hours'}</t>
+          <t>16-24 hours</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'too_small'}</t>
+          <t>too_small</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Too Small'}</t>
+          <t>Too Small</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Just Right'}</t>
+          <t>Just Right</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'too_large'}</t>
+          <t>too_large</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Too Large'}</t>
+          <t>Too Large</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'very_clear'}</t>
+          <t>very_clear</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Very Clear'}</t>
+          <t>Very Clear</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'very_confused'}</t>
+          <t>very_confused</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Very Confused'}</t>
+          <t>Very Confused</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'confused'}</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Confused'}</t>
+          <t>Confused</t>
         </is>
       </c>
     </row>
